--- a/syahadah.xlsx
+++ b/syahadah.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\syahadah-kelas-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08016294-10CF-4D9F-A919-A3ADA5727E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B915E12E-3DBC-4354-AAA1-1BB4050259C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{0B905FD0-EB53-4D0E-B8E6-78CC49293D85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B905FD0-EB53-4D0E-B8E6-78CC49293D85}"/>
   </bookViews>
   <sheets>
     <sheet name="syahadah" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">syahadah!$A$1:$I$26</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Nadil Al Fayyadh</t>
   </si>
@@ -92,6 +95,12 @@
   </si>
   <si>
     <t>Tanggal</t>
+  </si>
+  <si>
+    <t>Warna kuning = Data dari website</t>
+  </si>
+  <si>
+    <t>Warna merah = Data tidak ditemukan</t>
   </si>
 </sst>
 </file>
@@ -99,7 +108,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-421]dddd\,\ dd\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-421]dddd\,\ dd\ mmmm\ yyyy;@"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -249,7 +258,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,8 +450,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -572,6 +587,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -617,16 +669,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -638,10 +687,25 @@
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1019,556 +1083,448 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6439E1C-AE03-420F-90B4-EDC94398E7E4}">
-  <dimension ref="A1:O23"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8">
         <v>2</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2">
+      <c r="E2" s="8"/>
+      <c r="F2" s="8">
         <v>3</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2">
+      <c r="G2" s="8"/>
+      <c r="H2" s="8">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2">
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>45646</v>
+      </c>
+      <c r="C4" s="2">
         <v>5</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2">
-        <v>6</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2">
-        <v>7</v>
-      </c>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="D4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7">
+        <v>46050</v>
+      </c>
+      <c r="E5" s="2">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45458</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
         <v>45646</v>
       </c>
-      <c r="C4" s="9">
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46009</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>46154</v>
+      </c>
+      <c r="I6" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45819</v>
+      </c>
+      <c r="C8" s="2">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10">
+        <v>45646</v>
+      </c>
+      <c r="C10" s="2">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7">
+        <v>46144</v>
+      </c>
+      <c r="E10" s="2">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C13" s="2">
+        <v>17</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="B14" s="3">
+        <v>45819</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="7">
+        <v>46050</v>
+      </c>
+      <c r="E14" s="2">
+        <v>14</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3">
+        <v>45646</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3">
+        <v>46060</v>
+      </c>
+      <c r="E16" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8">
-        <v>46050</v>
-      </c>
-      <c r="E5" s="3">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="F16" s="3"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3">
+        <v>45819</v>
+      </c>
+      <c r="C17" s="2">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="3">
+        <v>45458</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>45646</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="7">
+        <v>46056</v>
+      </c>
+      <c r="G18" s="2">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7">
+        <v>46149</v>
+      </c>
+      <c r="E19" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="8">
-        <v>46154</v>
-      </c>
-      <c r="I6" s="3">
-        <v>13</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4">
-        <v>45819</v>
-      </c>
-      <c r="C8" s="9">
-        <v>12</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="8">
-        <v>46144</v>
-      </c>
-      <c r="E10" s="3">
-        <v>13</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4">
+      <c r="F19" s="3"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>45646</v>
+      </c>
+      <c r="C20" s="2">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3">
         <v>46009</v>
       </c>
-      <c r="C13" s="9">
-        <v>17</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="E20" s="2">
         <v>5</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="8">
-        <v>46050</v>
-      </c>
-      <c r="E14" s="3">
-        <v>14</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4">
-        <v>45646</v>
-      </c>
-      <c r="C16" s="9">
-        <v>5</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="8">
-        <v>46056</v>
-      </c>
-      <c r="G18" s="3">
-        <v>10</v>
-      </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8">
-        <v>46149</v>
-      </c>
-      <c r="E19" s="3">
-        <v>3</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="F20" s="3"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="6">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:O1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/syahadah.xlsx
+++ b/syahadah.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\syahadah-kelas-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B915E12E-3DBC-4354-AAA1-1BB4050259C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE306283-8EE9-4E53-8B59-0D7611D7A371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B905FD0-EB53-4D0E-B8E6-78CC49293D85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{0B905FD0-EB53-4D0E-B8E6-78CC49293D85}"/>
   </bookViews>
   <sheets>
     <sheet name="syahadah" sheetId="1" r:id="rId1"/>
+    <sheet name="Urut" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">syahadah!$A$1:$I$26</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="112">
   <si>
     <t>Nadil Al Fayyadh</t>
   </si>
@@ -101,6 +102,264 @@
   </si>
   <si>
     <t>Warna merah = Data tidak ditemukan</t>
+  </si>
+  <si>
+    <t>Urutan</t>
+  </si>
+  <si>
+    <t>Bulan Kelulusan</t>
+  </si>
+  <si>
+    <t>Tahun Kelulusan</t>
+  </si>
+  <si>
+    <t>Syahadah ke</t>
+  </si>
+  <si>
+    <t>Juznya</t>
+  </si>
+  <si>
+    <t>Nilai</t>
+  </si>
+  <si>
+    <t>Nomor Sertifikat</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Samarinda, 15 Juni 2024</t>
+  </si>
+  <si>
+    <t>Juz 1, 2, 3, 29, dan 30</t>
+  </si>
+  <si>
+    <t>MUMTAZ</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0010624</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0020624</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Samarinda, 20 Desember 2024</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0031224</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0041224</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>Juz 4, 5, 6, 7, dan 8</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0051224</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0061224</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0071224</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0081224</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0091224</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0101224</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0111224</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0121224</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0131224</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0141224</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>Samarinda, 11 Juni 2025</t>
+  </si>
+  <si>
+    <t>JAYYID JIDDAN</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0150625</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0160625</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0170625</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>Samarinda, 18 Desember 2025</t>
+  </si>
+  <si>
+    <t>Juz 9, 10, 11, 12, dan 13</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0181225</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0191225</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0201225</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>Samarinda, 28 Januari 2026</t>
+  </si>
+  <si>
+    <t>JAYYID</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0210126</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0220126</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>Samarinda, 3 Februari 2026</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0230226</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>Samarinda, 7 Februari 2026</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0240226</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>Samarinda, 2 Mei 2026</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0250526</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>Samarinda, 7 Mei 2026</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0260526</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>Samarinda, 12 Mei 2026</t>
+  </si>
+  <si>
+    <t>Juz 14, 15, 16, 17, dan 18</t>
+  </si>
+  <si>
+    <t>MAQBI 13.0270526</t>
   </si>
 </sst>
 </file>
@@ -110,7 +369,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-421]dddd\,\ dd\ mmmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,8 +516,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -456,8 +721,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -624,6 +894,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -669,7 +952,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -690,13 +973,13 @@
     <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -707,6 +990,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -753,7 +1039,57 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -764,6 +1100,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B814454B-DFE7-4BC7-818D-76B525D1D535}" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="A1:J28" xr:uid="{B814454B-DFE7-4BC7-818D-76B525D1D535}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{4A5D17FB-CBCB-4ABA-8E12-4F6CDA182869}" name="Urutan"/>
+    <tableColumn id="2" xr3:uid="{1A849872-6631-41A4-A13C-D957F72EA377}" name="Nama"/>
+    <tableColumn id="3" xr3:uid="{43B38EF8-5A56-413A-92C6-F01EBF94BCE8}" name="Syahadah ke"/>
+    <tableColumn id="4" xr3:uid="{F384241C-38D0-4648-BD87-131B366F6D7D}" name="Tanggal"/>
+    <tableColumn id="5" xr3:uid="{9CBCA536-92B4-4BB7-A569-B04BCB806FE7}" name="Kesalahan"/>
+    <tableColumn id="6" xr3:uid="{B1B30F00-DF89-43B2-837C-ED053519B59F}" name="Juznya"/>
+    <tableColumn id="7" xr3:uid="{C95A9C20-9328-46B1-BEDC-6CDC3BA3395F}" name="Nilai"/>
+    <tableColumn id="8" xr3:uid="{B478B1A7-A69D-4F6A-A143-A190F0FC3B45}" name="Bulan Kelulusan"/>
+    <tableColumn id="9" xr3:uid="{D4EB454D-BF17-4EE1-9BA3-192EB9DAC28C}" name="Tahun Kelulusan"/>
+    <tableColumn id="10" xr3:uid="{3A1DC453-F345-4680-BBFB-ADC981AFA2B5}" name="Nomor Sertifikat"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1101,7 +1456,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -1116,26 +1471,26 @@
       <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10">
         <v>2</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10">
         <v>3</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8">
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
         <v>4</v>
       </c>
-      <c r="I2" s="8"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+      <c r="A3" s="10"/>
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1182,8 +1537,12 @@
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
+      <c r="B5" s="9">
+        <v>45646</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
       <c r="D5" s="7">
         <v>46050</v>
       </c>
@@ -1228,8 +1587,12 @@
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
+      <c r="B7" s="9">
+        <v>45646</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="2"/>
       <c r="F7" s="3"/>
@@ -1258,8 +1621,12 @@
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
+      <c r="B9" s="9">
+        <v>45646</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="2"/>
       <c r="F9" s="3"/>
@@ -1271,7 +1638,7 @@
       <c r="A10" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>45646</v>
       </c>
       <c r="C10" s="2">
@@ -1292,8 +1659,12 @@
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="9">
+        <v>45646</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="2"/>
       <c r="F11" s="3"/>
@@ -1432,8 +1803,12 @@
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="9">
+        <v>45646</v>
+      </c>
+      <c r="C19" s="2">
+        <v>5</v>
+      </c>
       <c r="D19" s="7">
         <v>46149</v>
       </c>
@@ -1496,8 +1871,12 @@
       <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2"/>
+      <c r="B23" s="9">
+        <v>45646</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="2"/>
       <c r="F23" s="3"/>
@@ -1506,12 +1885,12 @@
       <c r="I23" s="2"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1527,4 +1906,925 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214D86E4-C66B-4802-98AC-0F8D689B3B85}">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>72</v>
+      </c>
+      <c r="J18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" t="s">
+        <v>72</v>
+      </c>
+      <c r="J21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" t="s">
+        <v>90</v>
+      </c>
+      <c r="J22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" t="s">
+        <v>90</v>
+      </c>
+      <c r="J23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" t="s">
+        <v>103</v>
+      </c>
+      <c r="I26" t="s">
+        <v>90</v>
+      </c>
+      <c r="J26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" t="s">
+        <v>90</v>
+      </c>
+      <c r="J27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" t="s">
+        <v>103</v>
+      </c>
+      <c r="I28" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/syahadah.xlsx
+++ b/syahadah.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\syahadah-kelas-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE306283-8EE9-4E53-8B59-0D7611D7A371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5DAD5A-427C-4297-BD02-33E672121BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{0B905FD0-EB53-4D0E-B8E6-78CC49293D85}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="120">
   <si>
     <t>Nadil Al Fayyadh</t>
   </si>
@@ -360,6 +360,30 @@
   </si>
   <si>
     <t>MAQBI 13.0270526</t>
+  </si>
+  <si>
+    <t>Deskripsi Pencapaian</t>
+  </si>
+  <si>
+    <t>Telah menyelesaikan dan menyetorkan hafalan Al-Quran 5 juz (Juz 1, 2, 3, 29, dan 30) di hadapan penguji dengan nilai MUMTAZ</t>
+  </si>
+  <si>
+    <t>Telah menyelesaikan dan menyetorkan hafalan Al-Quran 5 juz (Juz 4, 5, 6, 7, dan 8) di hadapan penguji dengan nilai MUMTAZ</t>
+  </si>
+  <si>
+    <t>Telah menyelesaikan dan menyetorkan hafalan Al-Quran 5 juz (Juz 9, 10, 11, 12, dan 13) di hadapan penguji dengan nilai MUMTAZ</t>
+  </si>
+  <si>
+    <t>Telah menyelesaikan dan menyetorkan hafalan Al-Quran 5 juz (Juz 4, 5, 6, 7, dan 8) di hadapan penguji dengan nilai JAYYID JIDDAN</t>
+  </si>
+  <si>
+    <t>Telah menyelesaikan dan menyetorkan hafalan Al-Quran 5 juz (Juz 14, 15, 16, 17, dan 18) di hadapan penguji dengan nilai JAYYID JIDDAN</t>
+  </si>
+  <si>
+    <t>Telah menyelesaikan dan menyetorkan hafalan Al-Quran 5 juz (Juz 1, 2, 3, 29, dan 30) di hadapan penguji dengan nilai JAYYID JIDDAN</t>
+  </si>
+  <si>
+    <t>Telah menyelesaikan dan menyetorkan hafalan Al-Quran 5 juz (Juz 4, 5, 6, 7, dan 8) di hadapan penguji dengan nilai JAYYID</t>
   </si>
 </sst>
 </file>
@@ -523,7 +547,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,6 +748,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -952,7 +982,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -979,6 +1009,9 @@
     <xf numFmtId="164" fontId="17" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -991,7 +1024,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1042,16 +1075,16 @@
   <dxfs count="3">
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1103,9 +1136,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B814454B-DFE7-4BC7-818D-76B525D1D535}" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
-  <autoFilter ref="A1:J28" xr:uid="{B814454B-DFE7-4BC7-818D-76B525D1D535}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B814454B-DFE7-4BC7-818D-76B525D1D535}" name="Table1" displayName="Table1" ref="A1:K28" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:K28" xr:uid="{B814454B-DFE7-4BC7-818D-76B525D1D535}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4A5D17FB-CBCB-4ABA-8E12-4F6CDA182869}" name="Urutan"/>
     <tableColumn id="2" xr3:uid="{1A849872-6631-41A4-A13C-D957F72EA377}" name="Nama"/>
     <tableColumn id="3" xr3:uid="{43B38EF8-5A56-413A-92C6-F01EBF94BCE8}" name="Syahadah ke"/>
@@ -1116,6 +1149,7 @@
     <tableColumn id="8" xr3:uid="{B478B1A7-A69D-4F6A-A143-A190F0FC3B45}" name="Bulan Kelulusan"/>
     <tableColumn id="9" xr3:uid="{D4EB454D-BF17-4EE1-9BA3-192EB9DAC28C}" name="Tahun Kelulusan"/>
     <tableColumn id="10" xr3:uid="{3A1DC453-F345-4680-BBFB-ADC981AFA2B5}" name="Nomor Sertifikat"/>
+    <tableColumn id="11" xr3:uid="{D0CDEBFD-29A4-417D-B507-B82B00F32C03}" name="Deskripsi Pencapaian"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1456,41 +1490,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="14"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11">
         <v>1</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11">
         <v>2</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11">
         <v>3</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
+      <c r="G2" s="11"/>
+      <c r="H2" s="11">
         <v>4</v>
       </c>
-      <c r="I2" s="10"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1910,7 +1944,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214D86E4-C66B-4802-98AC-0F8D689B3B85}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -1923,41 +1957,45 @@
     <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="126.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1988,8 +2026,11 @@
       <c r="J2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2020,8 +2061,11 @@
       <c r="J3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -2052,8 +2096,11 @@
       <c r="J4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -2084,8 +2131,11 @@
       <c r="J5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -2116,8 +2166,11 @@
       <c r="J6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -2148,8 +2201,11 @@
       <c r="J7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2180,8 +2236,11 @@
       <c r="J8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -2212,8 +2271,11 @@
       <c r="J9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -2244,8 +2306,11 @@
       <c r="J10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -2276,8 +2341,11 @@
       <c r="J11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2308,8 +2376,11 @@
       <c r="J12" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -2340,8 +2411,11 @@
       <c r="J13" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -2372,8 +2446,11 @@
       <c r="J14" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -2404,8 +2481,11 @@
       <c r="J15" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -2436,8 +2516,11 @@
       <c r="J16" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -2468,8 +2551,11 @@
       <c r="J17" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -2500,8 +2586,11 @@
       <c r="J18" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -2532,8 +2621,11 @@
       <c r="J19" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -2564,8 +2656,11 @@
       <c r="J20" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -2596,8 +2691,11 @@
       <c r="J21" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -2628,8 +2726,11 @@
       <c r="J22" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>92</v>
       </c>
@@ -2660,8 +2761,11 @@
       <c r="J23" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -2692,8 +2796,11 @@
       <c r="J24" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -2724,8 +2831,11 @@
       <c r="J25" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -2756,8 +2866,11 @@
       <c r="J26" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>105</v>
       </c>
@@ -2788,8 +2901,11 @@
       <c r="J27" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>108</v>
       </c>
@@ -2819,6 +2935,9 @@
       </c>
       <c r="J28" t="s">
         <v>111</v>
+      </c>
+      <c r="K28" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/syahadah.xlsx
+++ b/syahadah.xlsx
@@ -1012,6 +1012,9 @@
     <xf numFmtId="0" fontId="20" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1023,9 +1026,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1490,41 +1490,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12">
         <v>2</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12">
         <v>3</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12">
         <v>4</v>
       </c>
-      <c r="I2" s="11"/>
+      <c r="I2" s="12"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
+      <c r="A3" s="12"/>
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1991,7 +1991,7 @@
       <c r="J1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="11" t="s">
         <v>112</v>
       </c>
     </row>
